--- a/public/templates/CITYBUS-BAO-CAO-CAMERA-BP-QLCL-DV.xlsx
+++ b/public/templates/CITYBUS-BAO-CAO-CAMERA-BP-QLCL-DV.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/duykha/Workspace/reactjs/qlcldv/public/templates/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{032D8452-3DC7-254C-ABD0-479D6E96E3FD}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A767B5B9-E46F-9C40-AAC4-3790F9EF5DCB}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="24000" windowHeight="15240" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -315,78 +315,75 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyBorder="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -708,403 +705,420 @@
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="5.1640625" customWidth="1"/>
-    <col min="2" max="2" width="22.5" style="9" customWidth="1"/>
+    <col min="2" max="2" width="22.5" style="1" customWidth="1"/>
     <col min="3" max="3" width="41.1640625" customWidth="1"/>
     <col min="4" max="4" width="26.5" customWidth="1"/>
     <col min="5" max="6" width="23.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" s="10" customFormat="1" ht="33" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1" s="8" t="s">
+    <row r="1" spans="1:10" s="2" customFormat="1" ht="33" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A1" s="22" t="s">
         <v>17</v>
       </c>
-      <c r="B1" s="8"/>
-      <c r="C1" s="8"/>
-      <c r="D1" s="8"/>
-      <c r="E1" s="8"/>
-      <c r="F1" s="8"/>
-    </row>
-    <row r="2" spans="1:10" s="10" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A2" s="8"/>
-      <c r="B2" s="8"/>
-      <c r="C2" s="8"/>
-      <c r="D2" s="8"/>
-      <c r="E2" s="8"/>
-      <c r="F2" s="8"/>
-    </row>
-    <row r="3" spans="1:10" s="10" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A3" s="7" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="7"/>
-      <c r="C3" s="7"/>
-      <c r="D3" s="7"/>
-      <c r="E3" s="7"/>
-      <c r="F3" s="7"/>
-    </row>
-    <row r="4" spans="1:10" s="10" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A4" s="6" t="s">
+      <c r="B1" s="22"/>
+      <c r="C1" s="22"/>
+      <c r="D1" s="22"/>
+      <c r="E1" s="22"/>
+      <c r="F1" s="22"/>
+    </row>
+    <row r="2" spans="1:10" s="2" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A2" s="22"/>
+      <c r="B2" s="22"/>
+      <c r="C2" s="22"/>
+      <c r="D2" s="22"/>
+      <c r="E2" s="22"/>
+      <c r="F2" s="22"/>
+    </row>
+    <row r="3" spans="1:10" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A3" s="23" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="23"/>
+      <c r="C3" s="23"/>
+      <c r="D3" s="23"/>
+      <c r="E3" s="23"/>
+      <c r="F3" s="23"/>
+    </row>
+    <row r="4" spans="1:10" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A4" s="17" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="6"/>
-      <c r="C4" s="6"/>
-      <c r="D4" s="6"/>
-      <c r="E4" s="6"/>
-      <c r="F4" s="6"/>
-    </row>
-    <row r="5" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A5" s="6" t="s">
+      <c r="B4" s="17"/>
+      <c r="C4" s="17"/>
+      <c r="D4" s="17"/>
+      <c r="E4" s="17"/>
+      <c r="F4" s="17"/>
+    </row>
+    <row r="5" spans="1:10" s="2" customFormat="1" ht="24.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A5" s="17" t="s">
         <v>2</v>
       </c>
-      <c r="B5" s="6"/>
-      <c r="C5" s="6"/>
-      <c r="D5" s="6"/>
-      <c r="E5" s="6"/>
-      <c r="F5" s="6"/>
-    </row>
-    <row r="6" spans="1:10" s="10" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A6" s="5" t="s">
+      <c r="B5" s="17"/>
+      <c r="C5" s="17"/>
+      <c r="D5" s="17"/>
+      <c r="E5" s="17"/>
+      <c r="F5" s="17"/>
+    </row>
+    <row r="6" spans="1:10" s="2" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A6" s="21" t="s">
         <v>3</v>
       </c>
-      <c r="B6" s="5" t="s">
+      <c r="B6" s="21" t="s">
         <v>4</v>
       </c>
-      <c r="C6" s="5" t="s">
+      <c r="C6" s="21" t="s">
         <v>5</v>
       </c>
-      <c r="D6" s="5"/>
-      <c r="E6" s="5"/>
-      <c r="F6" s="5"/>
-    </row>
-    <row r="7" spans="1:10" s="10" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A7" s="5"/>
-      <c r="B7" s="5"/>
-      <c r="C7" s="11" t="s">
+      <c r="D6" s="21"/>
+      <c r="E6" s="21"/>
+      <c r="F6" s="21"/>
+    </row>
+    <row r="7" spans="1:10" s="2" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A7" s="21"/>
+      <c r="B7" s="21"/>
+      <c r="C7" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="D7" s="12" t="s">
+      <c r="D7" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="E7" s="12" t="s">
+      <c r="E7" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="F7" s="12" t="s">
+      <c r="F7" s="4" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="8" spans="1:10" s="10" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="13"/>
-      <c r="B8" s="14"/>
-      <c r="C8" s="15"/>
-      <c r="D8" s="16"/>
-      <c r="E8" s="16"/>
-      <c r="F8" s="16"/>
-    </row>
-    <row r="9" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A9" s="4" t="s">
+    <row r="8" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A8" s="5"/>
+      <c r="B8" s="9"/>
+      <c r="C8" s="6"/>
+      <c r="D8" s="7"/>
+      <c r="E8" s="7"/>
+      <c r="F8" s="7"/>
+    </row>
+    <row r="9" spans="1:10" s="2" customFormat="1" ht="24.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A9" s="16" t="s">
         <v>10</v>
       </c>
-      <c r="B9" s="4"/>
-      <c r="C9" s="17">
+      <c r="B9" s="16"/>
+      <c r="C9" s="8">
         <f>SUM(C8)</f>
         <v>0</v>
       </c>
-      <c r="D9" s="17">
+      <c r="D9" s="8">
         <f>SUM(D8)</f>
         <v>0</v>
       </c>
-      <c r="E9" s="17">
+      <c r="E9" s="8">
         <f>SUM(E8)</f>
         <v>0</v>
       </c>
-      <c r="F9" s="17">
+      <c r="F9" s="8">
         <f>SUM(F8)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A10" s="6" t="s">
+    <row r="10" spans="1:10" s="2" customFormat="1" ht="24.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A10" s="17" t="s">
         <v>11</v>
       </c>
-      <c r="B10" s="6"/>
-      <c r="C10" s="6"/>
-      <c r="D10" s="6"/>
-      <c r="E10" s="6"/>
-      <c r="F10" s="6"/>
-    </row>
-    <row r="11" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A11" s="5" t="s">
+      <c r="B10" s="17"/>
+      <c r="C10" s="17"/>
+      <c r="D10" s="17"/>
+      <c r="E10" s="17"/>
+      <c r="F10" s="17"/>
+    </row>
+    <row r="11" spans="1:10" s="2" customFormat="1" ht="24.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A11" s="21" t="s">
         <v>3</v>
       </c>
-      <c r="B11" s="5" t="s">
+      <c r="B11" s="21" t="s">
         <v>4</v>
       </c>
-      <c r="C11" s="5" t="s">
+      <c r="C11" s="21" t="s">
         <v>5</v>
       </c>
-      <c r="D11" s="5"/>
-      <c r="E11" s="5"/>
-      <c r="F11" s="5"/>
-    </row>
-    <row r="12" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A12" s="5"/>
-      <c r="B12" s="5"/>
-      <c r="C12" s="11" t="s">
+      <c r="D11" s="21"/>
+      <c r="E11" s="21"/>
+      <c r="F11" s="21"/>
+    </row>
+    <row r="12" spans="1:10" s="2" customFormat="1" ht="24.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A12" s="21"/>
+      <c r="B12" s="21"/>
+      <c r="C12" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="D12" s="12" t="s">
+      <c r="D12" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="E12" s="12" t="s">
+      <c r="E12" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="F12" s="12" t="s">
+      <c r="F12" s="4" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="13" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A13" s="13"/>
-      <c r="B13" s="18"/>
-      <c r="C13" s="16"/>
-      <c r="D13" s="16"/>
-      <c r="E13" s="16"/>
-      <c r="F13" s="19"/>
-    </row>
-    <row r="14" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A14" s="4" t="s">
+    <row r="13" spans="1:10" s="2" customFormat="1" ht="24.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A13" s="5"/>
+      <c r="B13" s="9"/>
+      <c r="C13" s="7"/>
+      <c r="D13" s="7"/>
+      <c r="E13" s="7"/>
+      <c r="F13" s="10"/>
+    </row>
+    <row r="14" spans="1:10" s="2" customFormat="1" ht="24.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A14" s="16" t="s">
         <v>10</v>
       </c>
-      <c r="B14" s="4"/>
-      <c r="C14" s="17">
+      <c r="B14" s="16"/>
+      <c r="C14" s="8">
         <f>SUM(C13)</f>
         <v>0</v>
       </c>
-      <c r="D14" s="17">
+      <c r="D14" s="8">
         <f>SUM(D13)</f>
         <v>0</v>
       </c>
-      <c r="E14" s="17">
+      <c r="E14" s="8">
         <f>SUM(E13)</f>
         <v>0</v>
       </c>
-      <c r="F14" s="17">
+      <c r="F14" s="8">
         <f>SUM(F13)</f>
         <v>0</v>
       </c>
-      <c r="J14" s="20"/>
-    </row>
-    <row r="15" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A15" s="6" t="s">
+      <c r="J14" s="11"/>
+    </row>
+    <row r="15" spans="1:10" s="2" customFormat="1" ht="24.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A15" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="B15" s="6"/>
-      <c r="C15" s="6"/>
-      <c r="D15" s="6"/>
-      <c r="E15" s="6"/>
-      <c r="F15" s="6"/>
-    </row>
-    <row r="16" spans="1:10" s="10" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A16" s="5" t="s">
+      <c r="B15" s="17"/>
+      <c r="C15" s="17"/>
+      <c r="D15" s="17"/>
+      <c r="E15" s="17"/>
+      <c r="F15" s="17"/>
+    </row>
+    <row r="16" spans="1:10" s="2" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A16" s="21" t="s">
         <v>3</v>
       </c>
-      <c r="B16" s="5" t="s">
+      <c r="B16" s="21" t="s">
         <v>4</v>
       </c>
-      <c r="C16" s="5" t="s">
+      <c r="C16" s="21" t="s">
         <v>5</v>
       </c>
-      <c r="D16" s="5"/>
-      <c r="E16" s="5"/>
-      <c r="F16" s="5"/>
-    </row>
-    <row r="17" spans="1:6" s="10" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A17" s="5"/>
-      <c r="B17" s="5"/>
-      <c r="C17" s="11" t="s">
+      <c r="D16" s="21"/>
+      <c r="E16" s="21"/>
+      <c r="F16" s="21"/>
+    </row>
+    <row r="17" spans="1:6" s="2" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A17" s="21"/>
+      <c r="B17" s="21"/>
+      <c r="C17" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="D17" s="12" t="s">
+      <c r="D17" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="E17" s="12" t="s">
+      <c r="E17" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="F17" s="12" t="s">
+      <c r="F17" s="4" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="18" spans="1:6" s="10" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A18" s="13"/>
-      <c r="B18" s="18"/>
-      <c r="C18" s="16"/>
-      <c r="D18" s="16"/>
-      <c r="E18" s="21"/>
-      <c r="F18" s="21"/>
-    </row>
-    <row r="19" spans="1:6" s="10" customFormat="1" ht="24.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A19" s="3" t="s">
+    <row r="18" spans="1:6" s="2" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A18" s="5"/>
+      <c r="B18" s="9"/>
+      <c r="C18" s="7"/>
+      <c r="D18" s="7"/>
+      <c r="E18" s="12"/>
+      <c r="F18" s="12"/>
+    </row>
+    <row r="19" spans="1:6" s="2" customFormat="1" ht="24.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A19" s="19" t="s">
         <v>10</v>
       </c>
-      <c r="B19" s="3"/>
-      <c r="C19" s="22">
+      <c r="B19" s="19"/>
+      <c r="C19" s="13">
         <f>SUM(C18)</f>
         <v>0</v>
       </c>
-      <c r="D19" s="17">
+      <c r="D19" s="8">
         <f>SUM(D18)</f>
         <v>0</v>
       </c>
-      <c r="E19" s="17">
+      <c r="E19" s="8">
         <f>SUM(E18)</f>
         <v>0</v>
       </c>
-      <c r="F19" s="17">
+      <c r="F19" s="8">
         <f>SUM(F18)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:6" s="10" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A20" s="6" t="s">
+    <row r="20" spans="1:6" s="2" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A20" s="17" t="s">
         <v>13</v>
       </c>
-      <c r="B20" s="6"/>
-      <c r="C20" s="6"/>
-      <c r="D20" s="6"/>
-      <c r="E20" s="6"/>
-      <c r="F20" s="6"/>
-    </row>
-    <row r="21" spans="1:6" s="10" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A21" s="2" t="s">
+      <c r="B20" s="17"/>
+      <c r="C20" s="17"/>
+      <c r="D20" s="17"/>
+      <c r="E20" s="17"/>
+      <c r="F20" s="17"/>
+    </row>
+    <row r="21" spans="1:6" s="2" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A21" s="20" t="s">
         <v>3</v>
       </c>
-      <c r="B21" s="2" t="s">
+      <c r="B21" s="20" t="s">
         <v>4</v>
       </c>
-      <c r="C21" s="5" t="s">
+      <c r="C21" s="21" t="s">
         <v>5</v>
       </c>
-      <c r="D21" s="5"/>
-      <c r="E21" s="5"/>
-      <c r="F21" s="5"/>
-    </row>
-    <row r="22" spans="1:6" s="10" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A22" s="2"/>
-      <c r="B22" s="2"/>
-      <c r="C22" s="23" t="s">
+      <c r="D21" s="21"/>
+      <c r="E21" s="21"/>
+      <c r="F21" s="21"/>
+    </row>
+    <row r="22" spans="1:6" s="2" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A22" s="20"/>
+      <c r="B22" s="20"/>
+      <c r="C22" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="D22" s="24" t="s">
+      <c r="D22" s="15" t="s">
         <v>7</v>
       </c>
-      <c r="E22" s="24" t="s">
+      <c r="E22" s="15" t="s">
         <v>8</v>
       </c>
-      <c r="F22" s="24" t="s">
+      <c r="F22" s="15" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="23" spans="1:6" s="10" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A23" s="13"/>
-      <c r="B23" s="18"/>
-      <c r="C23" s="16"/>
-      <c r="D23" s="16"/>
-      <c r="E23" s="21"/>
-      <c r="F23" s="21"/>
-    </row>
-    <row r="24" spans="1:6" s="10" customFormat="1" ht="24.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A24" s="4" t="s">
+    <row r="23" spans="1:6" s="2" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A23" s="5"/>
+      <c r="B23" s="9"/>
+      <c r="C23" s="7"/>
+      <c r="D23" s="7"/>
+      <c r="E23" s="12"/>
+      <c r="F23" s="12"/>
+    </row>
+    <row r="24" spans="1:6" s="2" customFormat="1" ht="24.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A24" s="16" t="s">
         <v>10</v>
       </c>
-      <c r="B24" s="4"/>
-      <c r="C24" s="17">
+      <c r="B24" s="16"/>
+      <c r="C24" s="8">
         <f>SUM(C23)</f>
         <v>0</v>
       </c>
-      <c r="D24" s="17">
+      <c r="D24" s="8">
         <f>SUM(D23)</f>
         <v>0</v>
       </c>
-      <c r="E24" s="17">
+      <c r="E24" s="8">
         <f>SUM(E23)</f>
         <v>0</v>
       </c>
-      <c r="F24" s="17">
+      <c r="F24" s="8">
         <f>SUM(F23)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:6" s="10" customFormat="1" ht="24.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A25" s="6" t="s">
+    <row r="25" spans="1:6" s="2" customFormat="1" ht="24.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A25" s="17" t="s">
         <v>14</v>
       </c>
-      <c r="B25" s="6"/>
-      <c r="C25" s="6"/>
-      <c r="D25" s="6"/>
-      <c r="E25" s="6"/>
-      <c r="F25" s="6"/>
+      <c r="B25" s="17"/>
+      <c r="C25" s="17"/>
+      <c r="D25" s="17"/>
+      <c r="E25" s="17"/>
+      <c r="F25" s="17"/>
     </row>
     <row r="26" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A26" s="1" t="s">
+      <c r="A26" s="18" t="s">
         <v>15</v>
       </c>
-      <c r="B26" s="1"/>
-      <c r="C26" s="1"/>
-      <c r="D26" s="1" t="s">
+      <c r="B26" s="18"/>
+      <c r="C26" s="18"/>
+      <c r="D26" s="18" t="s">
         <v>16</v>
       </c>
-      <c r="E26" s="1"/>
-      <c r="F26" s="1"/>
+      <c r="E26" s="18"/>
+      <c r="F26" s="18"/>
     </row>
     <row r="27" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A27" s="1"/>
-      <c r="B27" s="1"/>
-      <c r="C27" s="1"/>
-      <c r="D27" s="1"/>
-      <c r="E27" s="1"/>
-      <c r="F27" s="1"/>
+      <c r="A27" s="18"/>
+      <c r="B27" s="18"/>
+      <c r="C27" s="18"/>
+      <c r="D27" s="18"/>
+      <c r="E27" s="18"/>
+      <c r="F27" s="18"/>
     </row>
     <row r="28" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A28" s="1"/>
-      <c r="B28" s="1"/>
-      <c r="C28" s="1"/>
-      <c r="D28" s="1"/>
-      <c r="E28" s="1"/>
-      <c r="F28" s="1"/>
+      <c r="A28" s="18"/>
+      <c r="B28" s="18"/>
+      <c r="C28" s="18"/>
+      <c r="D28" s="18"/>
+      <c r="E28" s="18"/>
+      <c r="F28" s="18"/>
     </row>
     <row r="29" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A29" s="1"/>
-      <c r="B29" s="1"/>
-      <c r="C29" s="1"/>
-      <c r="D29" s="1"/>
-      <c r="E29" s="1"/>
-      <c r="F29" s="1"/>
+      <c r="A29" s="18"/>
+      <c r="B29" s="18"/>
+      <c r="C29" s="18"/>
+      <c r="D29" s="18"/>
+      <c r="E29" s="18"/>
+      <c r="F29" s="18"/>
     </row>
     <row r="30" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A30" s="1"/>
-      <c r="B30" s="1"/>
-      <c r="C30" s="1"/>
-      <c r="D30" s="1"/>
-      <c r="E30" s="1"/>
-      <c r="F30" s="1"/>
+      <c r="A30" s="18"/>
+      <c r="B30" s="18"/>
+      <c r="C30" s="18"/>
+      <c r="D30" s="18"/>
+      <c r="E30" s="18"/>
+      <c r="F30" s="18"/>
     </row>
     <row r="31" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A31" s="1"/>
-      <c r="B31" s="1"/>
-      <c r="C31" s="1"/>
-      <c r="D31" s="1"/>
-      <c r="E31" s="1"/>
-      <c r="F31" s="1"/>
+      <c r="A31" s="18"/>
+      <c r="B31" s="18"/>
+      <c r="C31" s="18"/>
+      <c r="D31" s="18"/>
+      <c r="E31" s="18"/>
+      <c r="F31" s="18"/>
     </row>
     <row r="32" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A32" s="1"/>
-      <c r="B32" s="1"/>
-      <c r="C32" s="1"/>
-      <c r="D32" s="1"/>
-      <c r="E32" s="1"/>
-      <c r="F32" s="1"/>
+      <c r="A32" s="18"/>
+      <c r="B32" s="18"/>
+      <c r="C32" s="18"/>
+      <c r="D32" s="18"/>
+      <c r="E32" s="18"/>
+      <c r="F32" s="18"/>
     </row>
   </sheetData>
   <mergeCells count="26">
+    <mergeCell ref="A1:F2"/>
+    <mergeCell ref="A3:F3"/>
+    <mergeCell ref="A4:F4"/>
+    <mergeCell ref="A5:F5"/>
+    <mergeCell ref="A6:A7"/>
+    <mergeCell ref="B6:B7"/>
+    <mergeCell ref="C6:F6"/>
+    <mergeCell ref="A9:B9"/>
+    <mergeCell ref="A10:F10"/>
+    <mergeCell ref="A11:A12"/>
+    <mergeCell ref="B11:B12"/>
+    <mergeCell ref="C11:F11"/>
+    <mergeCell ref="A14:B14"/>
+    <mergeCell ref="A15:F15"/>
+    <mergeCell ref="A16:A17"/>
+    <mergeCell ref="B16:B17"/>
+    <mergeCell ref="C16:F16"/>
     <mergeCell ref="A24:B24"/>
     <mergeCell ref="A25:F25"/>
     <mergeCell ref="A26:C32"/>
@@ -1114,23 +1128,6 @@
     <mergeCell ref="A21:A22"/>
     <mergeCell ref="B21:B22"/>
     <mergeCell ref="C21:F21"/>
-    <mergeCell ref="A14:B14"/>
-    <mergeCell ref="A15:F15"/>
-    <mergeCell ref="A16:A17"/>
-    <mergeCell ref="B16:B17"/>
-    <mergeCell ref="C16:F16"/>
-    <mergeCell ref="A9:B9"/>
-    <mergeCell ref="A10:F10"/>
-    <mergeCell ref="A11:A12"/>
-    <mergeCell ref="B11:B12"/>
-    <mergeCell ref="C11:F11"/>
-    <mergeCell ref="A1:F2"/>
-    <mergeCell ref="A3:F3"/>
-    <mergeCell ref="A4:F4"/>
-    <mergeCell ref="A5:F5"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="B6:B7"/>
-    <mergeCell ref="C6:F6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
